--- a/Simulation/sim_results_nonlinear.xlsx
+++ b/Simulation/sim_results_nonlinear.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mobina\Marquette\FAE Codes\Simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB5EC62-034B-45E0-A2A2-FE6BF8A7A99C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9160CC60-622A-4AA7-9FC4-5BA6DF10F506}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="raw_results" sheetId="1" r:id="rId1"/>
-    <sheet name="summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
   <si>
     <t>rep</t>
   </si>
@@ -91,42 +90,12 @@
   <si>
     <t>nonlinear</t>
   </si>
-  <si>
-    <t>fpca_recon_relMSE_vs_clean_mean</t>
-  </si>
-  <si>
-    <t>fpca_recon_relMSE_vs_noisy_mean</t>
-  </si>
-  <si>
-    <t>fae_recon_relMSE_vs_clean_mean</t>
-  </si>
-  <si>
-    <t>fae_recon_relMSE_vs_noisy_mean</t>
-  </si>
-  <si>
-    <t>fpca_fore_relMSE_vs_clean_mean</t>
-  </si>
-  <si>
-    <t>fpca_fore_relMSE_vs_noisy_mean</t>
-  </si>
-  <si>
-    <t>fae_fore_relMSE_vs_clean_mean</t>
-  </si>
-  <si>
-    <t>fae_fore_relMSE_vs_noisy_mean</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>% Improvement</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,6 +126,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="5"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -170,11 +147,25 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -213,25 +204,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -276,11 +267,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>raw_results!$D$1</c:f>
+              <c:f>raw_results!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fpca_recon_relMSE_vs_noisy</c:v>
+                  <c:v>fpca_fore_relMSE_vs_noisy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -311,39 +302,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>raw_results!$D$2:$D$11</c:f>
+              <c:f>raw_results!$J$2:$J$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.1179208979010582</c:v>
+                  <c:v>0.31323465704917908</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1169584766030312</c:v>
+                  <c:v>0.25798434019088751</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1157919839024544</c:v>
+                  <c:v>0.34672245383262629</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1171812042593956</c:v>
+                  <c:v>0.31374442577362061</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1151580810546875</c:v>
+                  <c:v>0.35718494653701782</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1137378811836243</c:v>
+                  <c:v>0.35701656341552729</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1148221716284752</c:v>
+                  <c:v>0.3547782301902771</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1159492284059525</c:v>
+                  <c:v>0.3041209876537323</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.11933595687150959</c:v>
+                  <c:v>0.33292841911315918</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1186763793230057</c:v>
+                  <c:v>0.34722945094108582</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -351,7 +342,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D3EA-4D7D-BC74-22D56A8391FB}"/>
+              <c16:uniqueId val="{00000000-CD42-475E-B7AE-F4F1829C4E38}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -360,11 +351,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>raw_results!$F$1</c:f>
+              <c:f>raw_results!$L$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fae_recon_relMSE_vs_noisy</c:v>
+                  <c:v>fae_fore_relMSE_vs_noisy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -395,39 +386,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>raw_results!$F$2:$F$11</c:f>
+              <c:f>raw_results!$L$2:$L$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>6.386575847864151E-2</c:v>
+                  <c:v>0.11214000731706621</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.8035826086997986E-2</c:v>
+                  <c:v>0.13398635387420649</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.3025889694690704E-2</c:v>
+                  <c:v>0.18891565501689911</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.5178250670433044E-2</c:v>
+                  <c:v>0.18852619826793671</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.4780056476593018E-2</c:v>
+                  <c:v>0.22915491461753851</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.3933071196079247E-2</c:v>
+                  <c:v>0.20645107328891751</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.7535782903432853E-2</c:v>
+                  <c:v>0.2044535577297211</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.2181241810321808E-2</c:v>
+                  <c:v>0.16207726299762731</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.3784167617559433E-2</c:v>
+                  <c:v>0.17550039291381839</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.2704611122608185E-2</c:v>
+                  <c:v>0.20441041886806491</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -435,7 +426,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D3EA-4D7D-BC74-22D56A8391FB}"/>
+              <c16:uniqueId val="{00000001-CD42-475E-B7AE-F4F1829C4E38}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -449,11 +440,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="394888655"/>
-        <c:axId val="389299951"/>
+        <c:axId val="560989119"/>
+        <c:axId val="551047519"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="394888655"/>
+        <c:axId val="560989119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -495,7 +486,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="389299951"/>
+        <c:crossAx val="551047519"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -503,7 +494,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="389299951"/>
+        <c:axId val="551047519"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -554,7 +545,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="394888655"/>
+        <c:crossAx val="560989119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -666,11 +657,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>raw_results!$C$1</c:f>
+              <c:f>raw_results!$I$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fpca_recon_relMSE_vs_clean</c:v>
+                  <c:v>fpca_fore_relMSE_vs_clean</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -701,39 +692,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>raw_results!$C$2:$C$11</c:f>
+              <c:f>raw_results!$I$2:$I$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.1171822473406792</c:v>
+                  <c:v>0.31186255812644958</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.11615099012851721</c:v>
+                  <c:v>0.25703656673431402</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1149167120456696</c:v>
+                  <c:v>0.34426182508468628</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1164683997631073</c:v>
+                  <c:v>0.3124883770942688</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1144415736198425</c:v>
+                  <c:v>0.35608133673667908</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.11294893175363541</c:v>
+                  <c:v>0.3571808934211731</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.11407012492418291</c:v>
+                  <c:v>0.35140177607536321</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.11510952562093731</c:v>
+                  <c:v>0.3049609363079071</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1185525134205818</c:v>
+                  <c:v>0.33582955598831182</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.11788143217563631</c:v>
+                  <c:v>0.34834170341491699</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -741,7 +732,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A9C0-4F92-B666-5797FEFE06E6}"/>
+              <c16:uniqueId val="{00000000-1505-4CD9-8561-A8A007C6EC11}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -750,11 +741,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>raw_results!$E$1</c:f>
+              <c:f>raw_results!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fae_recon_relMSE_vs_clean</c:v>
+                  <c:v>fae_fore_relMSE_vs_clean</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -785,39 +776,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>raw_results!$E$2:$E$11</c:f>
+              <c:f>raw_results!$K$2:$K$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>6.3120119273662567E-2</c:v>
+                  <c:v>0.11139728128910061</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.730237603187561E-2</c:v>
+                  <c:v>0.129769042134285</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.2160102427005768E-2</c:v>
+                  <c:v>0.18879066407680509</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.4341759085655212E-2</c:v>
+                  <c:v>0.18534199893474579</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.3925817608833313E-2</c:v>
+                  <c:v>0.22757190465927121</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.3039955198764801E-2</c:v>
+                  <c:v>0.2074664235115051</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.6718040704727173E-2</c:v>
+                  <c:v>0.2031120955944061</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.1358854174613953E-2</c:v>
+                  <c:v>0.16242058575153351</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.2988404631614692E-2</c:v>
+                  <c:v>0.17321139574050901</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.1969209015369415E-2</c:v>
+                  <c:v>0.20595318078994751</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -825,7 +816,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A9C0-4F92-B666-5797FEFE06E6}"/>
+              <c16:uniqueId val="{00000001-1505-4CD9-8561-A8A007C6EC11}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -839,11 +830,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="394888655"/>
-        <c:axId val="389299951"/>
+        <c:axId val="560989119"/>
+        <c:axId val="551047519"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="394888655"/>
+        <c:axId val="560989119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -885,7 +876,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="389299951"/>
+        <c:crossAx val="551047519"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -893,7 +884,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="389299951"/>
+        <c:axId val="551047519"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -944,7 +935,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="394888655"/>
+        <c:crossAx val="560989119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1056,11 +1047,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>raw_results!$J$1</c:f>
+              <c:f>raw_results!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fpca_fore_relMSE_vs_noisy</c:v>
+                  <c:v>fpca_recon_relMSE_vs_noisy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1091,39 +1082,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>raw_results!$J$2:$J$11</c:f>
+              <c:f>raw_results!$D$2:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.31323465704917908</c:v>
+                  <c:v>0.1179208979010582</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25798434019088751</c:v>
+                  <c:v>0.1169584766030312</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.34672245383262629</c:v>
+                  <c:v>0.1157919839024544</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.31374442577362061</c:v>
+                  <c:v>0.1171812042593956</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.35718494653701782</c:v>
+                  <c:v>0.1151580810546875</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.35701656341552729</c:v>
+                  <c:v>0.1137378811836243</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3547782301902771</c:v>
+                  <c:v>0.1148221716284752</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3041209876537323</c:v>
+                  <c:v>0.1159492284059525</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.33292841911315918</c:v>
+                  <c:v>0.11933595687150959</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.34722945094108582</c:v>
+                  <c:v>0.1186763793230057</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1131,7 +1122,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-68AC-4AFC-BE4F-FB536FAE2D6B}"/>
+              <c16:uniqueId val="{00000000-DE46-42DD-A86B-D709C142CFC0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1140,11 +1131,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>raw_results!$L$1</c:f>
+              <c:f>raw_results!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fae_fore_relMSE_vs_noisy</c:v>
+                  <c:v>fae_recon_relMSE_vs_noisy</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1175,39 +1166,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>raw_results!$L$2:$L$11</c:f>
+              <c:f>raw_results!$F$2:$F$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.11214000731706621</c:v>
+                  <c:v>6.386575847864151E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.13398635387420649</c:v>
+                  <c:v>6.8035826086997986E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.18891565501689911</c:v>
+                  <c:v>7.3025889694690704E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.18852619826793671</c:v>
+                  <c:v>7.5178250670433044E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.22915491461753851</c:v>
+                  <c:v>6.4780056476593018E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.20645107328891751</c:v>
+                  <c:v>4.3933071196079247E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2044535577297211</c:v>
+                  <c:v>3.7535782903432853E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.16207726299762731</c:v>
+                  <c:v>6.2181241810321808E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.17550039291381839</c:v>
+                  <c:v>4.3784167617559433E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.20441041886806491</c:v>
+                  <c:v>8.2704611122608185E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1215,7 +1206,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-68AC-4AFC-BE4F-FB536FAE2D6B}"/>
+              <c16:uniqueId val="{00000001-DE46-42DD-A86B-D709C142CFC0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1229,11 +1220,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="460109439"/>
-        <c:axId val="457377151"/>
+        <c:axId val="560989119"/>
+        <c:axId val="551047519"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="460109439"/>
+        <c:axId val="560989119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1275,7 +1266,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="457377151"/>
+        <c:crossAx val="551047519"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1283,7 +1274,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="457377151"/>
+        <c:axId val="551047519"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1334,7 +1325,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460109439"/>
+        <c:crossAx val="560989119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1446,11 +1437,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>raw_results!$I$1</c:f>
+              <c:f>raw_results!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fpca_fore_relMSE_vs_clean</c:v>
+                  <c:v>fpca_recon_relMSE_vs_clean</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1481,39 +1472,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>raw_results!$I$2:$I$11</c:f>
+              <c:f>raw_results!$C$2:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.31186255812644958</c:v>
+                  <c:v>0.1171822473406792</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25703656673431402</c:v>
+                  <c:v>0.11615099012851721</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.34426182508468628</c:v>
+                  <c:v>0.1149167120456696</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3124883770942688</c:v>
+                  <c:v>0.1164683997631073</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.35608133673667908</c:v>
+                  <c:v>0.1144415736198425</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3571808934211731</c:v>
+                  <c:v>0.11294893175363541</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.35140177607536321</c:v>
+                  <c:v>0.11407012492418291</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3049609363079071</c:v>
+                  <c:v>0.11510952562093731</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.33582955598831182</c:v>
+                  <c:v>0.1185525134205818</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.34834170341491699</c:v>
+                  <c:v>0.11788143217563631</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1521,7 +1512,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7005-4CB1-A522-26D8DFDD5827}"/>
+              <c16:uniqueId val="{00000000-26D2-496C-ACFE-9A763A141652}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1530,11 +1521,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>raw_results!$K$1</c:f>
+              <c:f>raw_results!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fae_fore_relMSE_vs_clean</c:v>
+                  <c:v>fae_recon_relMSE_vs_clean</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1565,39 +1556,39 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>raw_results!$K$2:$K$11</c:f>
+              <c:f>raw_results!$E$2:$E$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.11139728128910061</c:v>
+                  <c:v>6.3120119273662567E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.129769042134285</c:v>
+                  <c:v>6.730237603187561E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.18879066407680509</c:v>
+                  <c:v>7.2160102427005768E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.18534199893474579</c:v>
+                  <c:v>7.4341759085655212E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.22757190465927121</c:v>
+                  <c:v>6.3925817608833313E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2074664235115051</c:v>
+                  <c:v>4.3039955198764801E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2031120955944061</c:v>
+                  <c:v>3.6718040704727173E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.16242058575153351</c:v>
+                  <c:v>6.1358854174613953E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.17321139574050901</c:v>
+                  <c:v>4.2988404631614692E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.20595318078994751</c:v>
+                  <c:v>8.1969209015369415E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1605,7 +1596,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7005-4CB1-A522-26D8DFDD5827}"/>
+              <c16:uniqueId val="{00000001-26D2-496C-ACFE-9A763A141652}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1619,11 +1610,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="461780975"/>
-        <c:axId val="457372575"/>
+        <c:axId val="560989119"/>
+        <c:axId val="551047519"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="461780975"/>
+        <c:axId val="560989119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1665,7 +1656,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="457372575"/>
+        <c:crossAx val="551047519"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1673,7 +1664,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="457372575"/>
+        <c:axId val="551047519"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1724,7 +1715,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="461780975"/>
+        <c:crossAx val="560989119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3987,23 +3978,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>12382</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>60007</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C976D715-85D1-4ABD-870E-DFEC68CE0408}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{172CD86F-D9DE-40AA-A199-92A0B967936C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4023,23 +4014,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E55BF10B-3ECB-491F-A000-DE279A43E251}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D31E903-6DE1-4708-B1FA-63E45CCAC081}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4061,27 +4052,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>12382</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>60007</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65FE78F2-67D9-4D2B-A1C8-8E8DA772F1E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02C06087-DCA0-4727-B28A-F98C5A19A588}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4097,27 +4090,29 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>363855</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>145732</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>59055</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>172402</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A11ACCEF-07D2-478C-8142-83ECB04745E1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E62A5B81-CF22-44EF-9CEB-EBB5D0348EC1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4422,85 +4417,77 @@
   <dimension ref="A1:V14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" customWidth="1"/>
-    <col min="3" max="4" width="8.88671875" style="8"/>
-    <col min="5" max="6" width="8.88671875" style="6"/>
-    <col min="9" max="10" width="8.88671875" style="8"/>
-    <col min="11" max="12" width="8.88671875" style="6"/>
-    <col min="14" max="15" width="5.77734375" customWidth="1"/>
-    <col min="16" max="16" width="3.33203125" customWidth="1"/>
-    <col min="17" max="17" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" style="9"/>
+    <col min="5" max="6" width="8.88671875" style="5"/>
+    <col min="9" max="10" width="8.88671875" style="9"/>
+    <col min="11" max="12" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="3" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:22" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4511,16 +4498,16 @@
       <c r="B2">
         <v>30001</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="9">
         <v>0.1171822473406792</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="9">
         <v>0.1179208979010582</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>6.3120119273662567E-2</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>6.386575847864151E-2</v>
       </c>
       <c r="G2">
@@ -4529,16 +4516,16 @@
       <c r="H2">
         <v>6.1066355556249619E-5</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="9">
         <v>0.31186255812644958</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="9">
         <v>0.31323465704917908</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>0.11139728128910061</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>0.11214000731706621</v>
       </c>
       <c r="M2" t="s">
@@ -4579,16 +4566,16 @@
       <c r="B3">
         <v>30002</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="9">
         <v>0.11615099012851721</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="9">
         <v>0.1169584766030312</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>6.730237603187561E-2</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>6.8035826086997986E-2</v>
       </c>
       <c r="G3">
@@ -4597,16 +4584,16 @@
       <c r="H3">
         <v>8.3444581832736731E-5</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="9">
         <v>0.25703656673431402</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="9">
         <v>0.25798434019088751</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>0.129769042134285</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>0.13398635387420649</v>
       </c>
       <c r="M3" t="s">
@@ -4647,16 +4634,16 @@
       <c r="B4">
         <v>30003</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="9">
         <v>0.1149167120456696</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="9">
         <v>0.1157919839024544</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>7.2160102427005768E-2</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>7.3025889694690704E-2</v>
       </c>
       <c r="G4">
@@ -4665,16 +4652,16 @@
       <c r="H4">
         <v>7.9037512477952987E-5</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="9">
         <v>0.34426182508468628</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="9">
         <v>0.34672245383262629</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>0.18879066407680509</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>0.18891565501689911</v>
       </c>
       <c r="M4" t="s">
@@ -4715,16 +4702,16 @@
       <c r="B5">
         <v>30004</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="9">
         <v>0.1164683997631073</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="9">
         <v>0.1171812042593956</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>7.4341759085655212E-2</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>7.5178250670433044E-2</v>
       </c>
       <c r="G5">
@@ -4733,16 +4720,16 @@
       <c r="H5">
         <v>9.2225694970693439E-5</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="9">
         <v>0.3124883770942688</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="9">
         <v>0.31374442577362061</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>0.18534199893474579</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>0.18852619826793671</v>
       </c>
       <c r="M5" t="s">
@@ -4783,16 +4770,16 @@
       <c r="B6">
         <v>30005</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="9">
         <v>0.1144415736198425</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <v>0.1151580810546875</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>6.3925817608833313E-2</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>6.4780056476593018E-2</v>
       </c>
       <c r="G6">
@@ -4801,16 +4788,16 @@
       <c r="H6">
         <v>1.0019254114013171E-4</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="9">
         <v>0.35608133673667908</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="9">
         <v>0.35718494653701782</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>0.22757190465927121</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>0.22915491461753851</v>
       </c>
       <c r="M6" t="s">
@@ -4851,16 +4838,16 @@
       <c r="B7">
         <v>30006</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <v>0.11294893175363541</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="9">
         <v>0.1137378811836243</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>4.3039955198764801E-2</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>4.3933071196079247E-2</v>
       </c>
       <c r="G7">
@@ -4869,16 +4856,16 @@
       <c r="H7">
         <v>9.5381918072234839E-5</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="9">
         <v>0.3571808934211731</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="9">
         <v>0.35701656341552729</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>0.2074664235115051</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>0.20645107328891751</v>
       </c>
       <c r="M7" t="s">
@@ -4919,16 +4906,16 @@
       <c r="B8">
         <v>30007</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="9">
         <v>0.11407012492418291</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="9">
         <v>0.1148221716284752</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>3.6718040704727173E-2</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>3.7535782903432853E-2</v>
       </c>
       <c r="G8">
@@ -4937,16 +4924,16 @@
       <c r="H8">
         <v>8.8646520453039557E-5</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="9">
         <v>0.35140177607536321</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="9">
         <v>0.3547782301902771</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>0.2031120955944061</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>0.2044535577297211</v>
       </c>
       <c r="M8" t="s">
@@ -4987,16 +4974,16 @@
       <c r="B9">
         <v>30008</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="9">
         <v>0.11510952562093731</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9">
         <v>0.1159492284059525</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>6.1358854174613953E-2</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>6.2181241810321808E-2</v>
       </c>
       <c r="G9">
@@ -5005,16 +4992,16 @@
       <c r="H9">
         <v>8.2167673099320382E-5</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="9">
         <v>0.3049609363079071</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="9">
         <v>0.3041209876537323</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>0.16242058575153351</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>0.16207726299762731</v>
       </c>
       <c r="M9" t="s">
@@ -5055,16 +5042,16 @@
       <c r="B10">
         <v>30009</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="9">
         <v>0.1185525134205818</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="9">
         <v>0.11933595687150959</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>4.2988404631614692E-2</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>4.3784167617559433E-2</v>
       </c>
       <c r="G10">
@@ -5073,16 +5060,16 @@
       <c r="H10">
         <v>7.7582393714692444E-5</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="9">
         <v>0.33582955598831182</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="9">
         <v>0.33292841911315918</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>0.17321139574050901</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>0.17550039291381839</v>
       </c>
       <c r="M10" t="s">
@@ -5123,16 +5110,16 @@
       <c r="B11">
         <v>30010</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="9">
         <v>0.11788143217563631</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="9">
         <v>0.1186763793230057</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>8.1969209015369415E-2</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>8.2704611122608185E-2</v>
       </c>
       <c r="G11">
@@ -5141,16 +5128,16 @@
       <c r="H11">
         <v>8.5684412624686956E-5</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="9">
         <v>0.34834170341491699</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="9">
         <v>0.34722945094108582</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>0.20595318078994751</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <v>0.20441041886806491</v>
       </c>
       <c r="M11" t="s">
@@ -5184,52 +5171,54 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="8">
+    <row r="13" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="10">
         <f>AVERAGE(C2:C11)</f>
         <v>0.11577224507927894</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="10">
         <f t="shared" ref="D13:F13" si="0">AVERAGE(D2:D11)</f>
         <v>0.11655322611331942</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <f t="shared" si="0"/>
         <v>6.0692463815212247E-2</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <f t="shared" si="0"/>
         <v>6.150246560573578E-2</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="10">
         <f>AVERAGE(I2:I11)</f>
         <v>0.32794455289840696</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="10">
         <f t="shared" ref="J13:L13" si="1">AVERAGE(J2:J11)</f>
         <v>0.32849444746971129</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="7">
         <f t="shared" si="1"/>
         <v>0.1795034572482109</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="7">
         <f t="shared" si="1"/>
         <v>0.18056158348917961</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="E14" s="3">
+        <f>(C13-E13)/C13</f>
+        <v>0.47575980949794106</v>
+      </c>
+      <c r="F14" s="3">
         <f>(D13-F13)/D13</f>
         <v>0.47232292355477384</v>
       </c>
-      <c r="L14" s="4">
+      <c r="K14" s="3">
+        <f>(I13-K13)/I13</f>
+        <v>0.45264083314773401</v>
+      </c>
+      <c r="L14" s="3">
         <f>(J13-L13)/J13</f>
         <v>0.45033596494556205</v>
       </c>
@@ -5238,66 +5227,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>0.1157722450792789</v>
-      </c>
-      <c r="B2">
-        <v>0.11655322611331941</v>
-      </c>
-      <c r="C2">
-        <v>6.0692463815212247E-2</v>
-      </c>
-      <c r="D2">
-        <v>6.150246560573578E-2</v>
-      </c>
-      <c r="E2">
-        <v>0.32794455289840702</v>
-      </c>
-      <c r="F2">
-        <v>0.32849444746971129</v>
-      </c>
-      <c r="G2">
-        <v>0.1795034572482109</v>
-      </c>
-      <c r="H2">
-        <v>0.18056158348917961</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Simulation/sim_results_nonlinear.xlsx
+++ b/Simulation/sim_results_nonlinear.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mobina\Marquette\FAE Codes\Simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9160CC60-622A-4AA7-9FC4-5BA6DF10F506}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B7D199-37F6-4E42-9C2A-9CC1DD24CA2E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,6 +95,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -204,7 +207,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -218,12 +221,13 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4417,9 +4421,9 @@
   <dimension ref="A1:V14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="4" width="8.88671875" style="9"/>
+    <col min="3" max="4" width="8.88671875" style="8"/>
     <col min="5" max="6" width="8.88671875" style="5"/>
-    <col min="9" max="10" width="8.88671875" style="9"/>
+    <col min="9" max="10" width="8.88671875" style="8"/>
     <col min="11" max="12" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
@@ -4430,10 +4434,10 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -4448,10 +4452,10 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4498,10 +4502,10 @@
       <c r="B2">
         <v>30001</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>0.1171822473406792</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>0.1179208979010582</v>
       </c>
       <c r="E2" s="5">
@@ -4516,10 +4520,10 @@
       <c r="H2">
         <v>6.1066355556249619E-5</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="8">
         <v>0.31186255812644958</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="8">
         <v>0.31323465704917908</v>
       </c>
       <c r="K2" s="5">
@@ -4544,7 +4548,7 @@
         <v>1E-3</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S2">
         <v>5</v>
@@ -4566,10 +4570,10 @@
       <c r="B3">
         <v>30002</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>0.11615099012851721</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>0.1169584766030312</v>
       </c>
       <c r="E3" s="5">
@@ -4584,10 +4588,10 @@
       <c r="H3">
         <v>8.3444581832736731E-5</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>0.25703656673431402</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="8">
         <v>0.25798434019088751</v>
       </c>
       <c r="K3" s="5">
@@ -4612,7 +4616,7 @@
         <v>1E-3</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3">
         <v>5</v>
@@ -4634,10 +4638,10 @@
       <c r="B4">
         <v>30003</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>0.1149167120456696</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>0.1157919839024544</v>
       </c>
       <c r="E4" s="5">
@@ -4652,10 +4656,10 @@
       <c r="H4">
         <v>7.9037512477952987E-5</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <v>0.34426182508468628</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="8">
         <v>0.34672245383262629</v>
       </c>
       <c r="K4" s="5">
@@ -4680,7 +4684,7 @@
         <v>1E-3</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S4">
         <v>5</v>
@@ -4702,10 +4706,10 @@
       <c r="B5">
         <v>30004</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>0.1164683997631073</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>0.1171812042593956</v>
       </c>
       <c r="E5" s="5">
@@ -4720,10 +4724,10 @@
       <c r="H5">
         <v>9.2225694970693439E-5</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>0.3124883770942688</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>0.31374442577362061</v>
       </c>
       <c r="K5" s="5">
@@ -4748,7 +4752,7 @@
         <v>1E-3</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S5">
         <v>5</v>
@@ -4770,10 +4774,10 @@
       <c r="B6">
         <v>30005</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>0.1144415736198425</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>0.1151580810546875</v>
       </c>
       <c r="E6" s="5">
@@ -4788,10 +4792,10 @@
       <c r="H6">
         <v>1.0019254114013171E-4</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <v>0.35608133673667908</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>0.35718494653701782</v>
       </c>
       <c r="K6" s="5">
@@ -4816,7 +4820,7 @@
         <v>1E-3</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S6">
         <v>5</v>
@@ -4838,10 +4842,10 @@
       <c r="B7">
         <v>30006</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>0.11294893175363541</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>0.1137378811836243</v>
       </c>
       <c r="E7" s="5">
@@ -4856,10 +4860,10 @@
       <c r="H7">
         <v>9.5381918072234839E-5</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>0.3571808934211731</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>0.35701656341552729</v>
       </c>
       <c r="K7" s="5">
@@ -4884,7 +4888,7 @@
         <v>1E-3</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S7">
         <v>5</v>
@@ -4906,10 +4910,10 @@
       <c r="B8">
         <v>30007</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>0.11407012492418291</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>0.1148221716284752</v>
       </c>
       <c r="E8" s="5">
@@ -4924,10 +4928,10 @@
       <c r="H8">
         <v>8.8646520453039557E-5</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <v>0.35140177607536321</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <v>0.3547782301902771</v>
       </c>
       <c r="K8" s="5">
@@ -4952,7 +4956,7 @@
         <v>1E-3</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S8">
         <v>5</v>
@@ -4974,10 +4978,10 @@
       <c r="B9">
         <v>30008</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>0.11510952562093731</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>0.1159492284059525</v>
       </c>
       <c r="E9" s="5">
@@ -4992,10 +4996,10 @@
       <c r="H9">
         <v>8.2167673099320382E-5</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <v>0.3049609363079071</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>0.3041209876537323</v>
       </c>
       <c r="K9" s="5">
@@ -5020,7 +5024,7 @@
         <v>1E-3</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S9">
         <v>5</v>
@@ -5042,10 +5046,10 @@
       <c r="B10">
         <v>30009</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>0.1185525134205818</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>0.11933595687150959</v>
       </c>
       <c r="E10" s="5">
@@ -5060,10 +5064,10 @@
       <c r="H10">
         <v>7.7582393714692444E-5</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>0.33582955598831182</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>0.33292841911315918</v>
       </c>
       <c r="K10" s="5">
@@ -5088,7 +5092,7 @@
         <v>1E-3</v>
       </c>
       <c r="R10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S10">
         <v>5</v>
@@ -5110,10 +5114,10 @@
       <c r="B11">
         <v>30010</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>0.11788143217563631</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>0.1186763793230057</v>
       </c>
       <c r="E11" s="5">
@@ -5128,10 +5132,10 @@
       <c r="H11">
         <v>8.5684412624686956E-5</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <v>0.34834170341491699</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>0.34722945094108582</v>
       </c>
       <c r="K11" s="5">
@@ -5156,7 +5160,7 @@
         <v>1E-3</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S11">
         <v>5</v>
@@ -5172,35 +5176,37 @@
       </c>
     </row>
     <row r="13" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <f>AVERAGE(C2:C11)</f>
         <v>0.11577224507927894</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <f t="shared" ref="D13:F13" si="0">AVERAGE(D2:D11)</f>
         <v>0.11655322611331942</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="10">
         <f t="shared" si="0"/>
         <v>6.0692463815212247E-2</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="10">
         <f t="shared" si="0"/>
         <v>6.150246560573578E-2</v>
       </c>
-      <c r="I13" s="10">
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="9">
         <f>AVERAGE(I2:I11)</f>
         <v>0.32794455289840696</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="9">
         <f t="shared" ref="J13:L13" si="1">AVERAGE(J2:J11)</f>
         <v>0.32849444746971129</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="10">
         <f t="shared" si="1"/>
         <v>0.1795034572482109</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="10">
         <f t="shared" si="1"/>
         <v>0.18056158348917961</v>
       </c>
